--- a/data/trans_orig/IP06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP06-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41652</t>
+          <t>41058</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57779</t>
+          <t>58335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41946</t>
+          <t>43534</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58199</t>
+          <t>58682</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88553</t>
+          <t>88842</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111467</t>
+          <t>111541</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42192</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58404</t>
+          <t>58810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>32281</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48779</t>
+          <t>47430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80128</t>
+          <t>79482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102830</t>
+          <t>102230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>25638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>40407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>28703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42947</t>
+          <t>43252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58398</t>
+          <t>58806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79353</t>
+          <t>79488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>40135</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55191</t>
+          <t>55107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38063</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52799</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81503</t>
+          <t>82075</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102986</t>
+          <t>103656</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20642</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33926</t>
+          <t>33853</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33677</t>
+          <t>32945</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52329</t>
+          <t>51251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41230</t>
+          <t>41346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53671</t>
+          <t>52747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59094</t>
+          <t>58587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74196</t>
+          <t>73289</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102313</t>
+          <t>102531</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121865</t>
+          <t>122921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33017</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37451</t>
+          <t>37085</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58867</t>
+          <t>57833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43053</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62494</t>
+          <t>62449</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38517</t>
+          <t>39003</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57546</t>
+          <t>58212</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>86590</t>
+          <t>85967</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>113417</t>
+          <t>115113</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111350</t>
+          <t>110919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132671</t>
+          <t>133852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>114289</t>
+          <t>115635</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136580</t>
+          <t>136966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>234342</t>
+          <t>231858</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>263623</t>
+          <t>263930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>29844</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>29536</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49173</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>554</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17590</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30886</t>
+          <t>30781</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>27552</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54717</t>
+          <t>54819</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>49689</t>
+          <t>48859</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>65487</t>
+          <t>65325</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>81149</t>
+          <t>80451</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>98152</t>
+          <t>96926</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>133238</t>
+          <t>134326</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>157058</t>
+          <t>157079</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>24838</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20795</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>25024</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>25196</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>42088</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42108</t>
+          <t>41836</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>55121</t>
+          <t>54962</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36997</t>
+          <t>36915</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50464</t>
+          <t>50295</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>84011</t>
+          <t>83144</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>102361</t>
+          <t>101995</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,56%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>57174</t>
+          <t>57554</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>84648</t>
+          <t>83787</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>47905</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>72834</t>
+          <t>72969</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>111867</t>
+          <t>111645</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>147934</t>
+          <t>146916</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19985</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>169777</t>
+          <t>167701</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>206567</t>
+          <t>205003</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>181571</t>
+          <t>182290</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>218896</t>
+          <t>219211</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>361802</t>
+          <t>361855</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>413596</t>
+          <t>412710</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>351858</t>
+          <t>352349</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>392363</t>
+          <t>394508</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>389838</t>
+          <t>390466</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>430540</t>
+          <t>430269</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>757042</t>
+          <t>756375</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>814127</t>
+          <t>812940</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>35924</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50900</t>
+          <t>50791</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49546</t>
+          <t>50023</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64014</t>
+          <t>63857</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>89016</t>
+          <t>89811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111567</t>
+          <t>112548</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36573</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52550</t>
+          <t>52413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22217</t>
+          <t>22356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>36165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63170</t>
+          <t>62621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84421</t>
+          <t>84724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>34156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49122</t>
+          <t>49889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28447</t>
+          <t>28121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43481</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65698</t>
+          <t>66061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87625</t>
+          <t>88267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>38226</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>54316</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46513</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62468</t>
+          <t>62034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89807</t>
+          <t>89554</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111971</t>
+          <t>112338</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18677</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32841</t>
+          <t>33057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18713</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>32895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42034</t>
+          <t>41995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61493</t>
+          <t>61278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46153</t>
+          <t>45957</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60713</t>
+          <t>61013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48490</t>
+          <t>49089</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63788</t>
+          <t>63819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98752</t>
+          <t>100106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120002</t>
+          <t>120205</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,46%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>25025</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>31505</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28787</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50211</t>
+          <t>50222</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>10984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37997</t>
+          <t>39315</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57000</t>
+          <t>58907</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52436</t>
+          <t>54001</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75823</t>
+          <t>75784</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>97276</t>
+          <t>99516</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128420</t>
+          <t>129452</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127327</t>
+          <t>127265</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>148958</t>
+          <t>149557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>122989</t>
+          <t>123605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148863</t>
+          <t>148496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257615</t>
+          <t>258453</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>290947</t>
+          <t>290201</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14467</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29884</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55408</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32678</t>
+          <t>32742</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37861</t>
+          <t>39018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44053</t>
+          <t>44663</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66554</t>
+          <t>67152</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>89301</t>
+          <t>90244</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107880</t>
+          <t>107894</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>77100</t>
+          <t>77435</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>96197</t>
+          <t>96518</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>172214</t>
+          <t>172384</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>199515</t>
+          <t>198675</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26375</t>
+          <t>27263</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>22288</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>37815</t>
+          <t>37708</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8133,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>32929</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>43972</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40491</t>
+          <t>40772</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54233</t>
+          <t>54145</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>78204</t>
+          <t>77708</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>95759</t>
+          <t>94582</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>40533</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>62559</t>
+          <t>63294</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>46060</t>
+          <t>46504</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>71919</t>
+          <t>70346</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>94357</t>
+          <t>93373</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>127038</t>
+          <t>127647</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>19277</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>21289</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19899</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36682</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>172831</t>
+          <t>172400</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>212187</t>
+          <t>212624</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>213553</t>
+          <t>212395</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>254538</t>
+          <t>253708</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>397678</t>
+          <t>397727</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>454943</t>
+          <t>452980</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>400926</t>
+          <t>402079</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>442296</t>
+          <t>443257</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>389852</t>
+          <t>389881</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>433651</t>
+          <t>434241</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>801209</t>
+          <t>800116</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>864862</t>
+          <t>862506</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,88%</t>
         </is>
       </c>
     </row>
@@ -9166,12 +9166,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25800</t>
+          <t>25971</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40244</t>
+          <t>40179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29155</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45219</t>
+          <t>45720</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60175</t>
+          <t>59856</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80890</t>
+          <t>80642</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>37736</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53233</t>
+          <t>52476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50253</t>
+          <t>49471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66878</t>
+          <t>66262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93442</t>
+          <t>93160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115197</t>
+          <t>115071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,92%</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9898,47 +9898,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>10750</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>10474</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23295</t>
+          <t>23769</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37762</t>
+          <t>38778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30998</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57887</t>
+          <t>58306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80956</t>
+          <t>80775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>61209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77619</t>
+          <t>76529</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56586</t>
+          <t>57218</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74228</t>
+          <t>74581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>122808</t>
+          <t>122955</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>146179</t>
+          <t>146730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10530,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10545,12 +10545,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26680</t>
+          <t>26541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27589</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>43128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49972</t>
+          <t>50051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>57148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85671</t>
+          <t>85223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102426</t>
+          <t>103880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>23818</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44719</t>
+          <t>43184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -11099,12 +11099,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40727</t>
+          <t>41567</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61403</t>
+          <t>61277</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28655</t>
+          <t>29142</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46286</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74115</t>
+          <t>73268</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>101187</t>
+          <t>100617</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11184,12 +11184,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -11212,12 +11212,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136539</t>
+          <t>137742</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160069</t>
+          <t>159955</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144553</t>
+          <t>145412</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164710</t>
+          <t>165782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>289602</t>
+          <t>290263</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>320915</t>
+          <t>321266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>28812</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33876</t>
+          <t>34324</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36115</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57798</t>
+          <t>57441</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14343</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27694</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11738,12 +11738,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>29260</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11781,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>79174</t>
+          <t>79516</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>97157</t>
+          <t>97903</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>87670</t>
+          <t>86217</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>105725</t>
+          <t>106347</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>171284</t>
+          <t>172621</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>199110</t>
+          <t>199438</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -12011,12 +12011,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22936</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25774</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37282</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>48826</t>
+          <t>49456</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12385,12 +12385,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>43314</t>
+          <t>43026</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>55490</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>83046</t>
+          <t>84710</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>100072</t>
+          <t>101398</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>42975</t>
+          <t>41920</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>66429</t>
+          <t>65372</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>49353</t>
+          <t>51077</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>74931</t>
+          <t>75636</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>98811</t>
+          <t>99143</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>132392</t>
+          <t>132395</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18290</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35308</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12778,12 +12778,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12806,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>140977</t>
+          <t>141174</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>176113</t>
+          <t>176293</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>141187</t>
+          <t>142177</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>178597</t>
+          <t>179140</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>293833</t>
+          <t>292128</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>343234</t>
+          <t>346000</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>422720</t>
+          <t>422369</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>462458</t>
+          <t>461505</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>456785</t>
+          <t>454556</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>497576</t>
+          <t>496773</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>890168</t>
+          <t>888149</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>947174</t>
+          <t>946602</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,73%</t>
         </is>
       </c>
     </row>
